--- a/research_materials/02_validation/checker_validation.xlsx
+++ b/research_materials/02_validation/checker_validation.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 21:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>

--- a/research_materials/02_validation/checker_validation.xlsx
+++ b/research_materials/02_validation/checker_validation.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>

--- a/research_materials/02_validation/checker_validation.xlsx
+++ b/research_materials/02_validation/checker_validation.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>

--- a/research_materials/02_validation/checker_validation.xlsx
+++ b/research_materials/02_validation/checker_validation.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:57 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
